--- a/reports/devops-juniors-israel-2026-W23.xlsx
+++ b/reports/devops-juniors-israel-2026-W23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="372">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-01T11:55:05</t>
+    <t xml:space="preserve">2026-06-02T10:54:26</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -103,6 +103,9 @@
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -112,6 +115,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">remoteok</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rank</t>
   </si>
   <si>
@@ -160,715 +166,712 @@
     <t xml:space="preserve">2026-05-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior AI SRE Developer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helfy</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyager Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMware System Administrator (36310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-system-administrator-36310-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4421685538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fortinet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regatta Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bria AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Service Desk Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zensar Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artivion EMEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Databases, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-artivion-emea-4423879474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gurugram, India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4418390308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plarium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4422886760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sela</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4413398653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-sela-4418758138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk JB-594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-confidential-4418731915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT HelpDesk Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAST Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-admin-at-vast-data-4401197444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITE123</t>
   </si>
   <si>
     <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4402893693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outpost24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-outpost24-4411657094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist - Tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orca AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-tier-2-at-orca-ai-4409854863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4406458748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4405103757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8553629002&amp;gh_jid=8553629002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4410129423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4418390308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LESICO Group LTD - קבוצת לסיכו בע"מ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-lesico-group-ltd-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9C%D7%A1%D7%99%D7%9B%D7%95-%D7%91%D7%A2-%D7%9E-4418718295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papaya Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-papaya-global-4418750824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Eng.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultra Information Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-eng-at-ultra-information-solutions-4412395476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GlassesUSA.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-engineer-at-varonis-4389733678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-log-on-software-4418731915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT HelpDesk Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAST Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-admin-at-vast-data-4401197444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
   </si>
   <si>
     <t xml:space="preserve">IT Operations Specialist</t>
@@ -883,9 +886,6 @@
     <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
     <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
   </si>
   <si>
@@ -898,7 +898,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
   </si>
   <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4419242661</t>
   </si>
   <si>
     <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
@@ -922,111 +928,99 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
   </si>
   <si>
-    <t xml:space="preserve">Systems Engineer - SiPh Test Solutions (Teradyne, Haifa, Israel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teradyne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-siph-test-solutions-teradyne-haifa-israel-at-teradyne-4416856875</t>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sderot, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4416075873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-spinomenal-4369538005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fireberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
   </si>
   <si>
     <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-south-apac-sea-anz-ind-subcont-4417601752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sderot, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4416075873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-spinomenal-4369538005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fireberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4418372549</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-plaee-4421385634</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Engineering Student</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
   </si>
   <si>
+    <t xml:space="preserve">Futuros Profesionales Trainee AutomatizaciÃ³n de Procesos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universia Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buenos Aires y alrededores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-futuros-profesionales-trainee-automatizacion-de-procesos-universia-argentina-1132661</t>
+  </si>
+  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -1045,37 +1039,46 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">AWS</t>
@@ -1084,28 +1087,16 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1126,6 +1117,9 @@
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jobs</t>
   </si>
   <si>
@@ -1136,9 +1130,6 @@
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">remoteok</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1254,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1271,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1279,7 +1270,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -1287,7 +1278,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -1369,7 +1360,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22">
@@ -1377,7 +1368,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1385,7 +1376,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1393,33 +1384,49 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-    </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3">
-        <v>65</v>
-      </c>
+      <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>10</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1431,7 +1438,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1443,34 +1450,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
@@ -1478,13 +1485,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>25</v>
@@ -1493,16 +1500,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -1510,31 +1517,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -1542,31 +1549,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1574,31 +1581,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1606,31 +1613,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
         <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1638,13 +1645,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
@@ -1653,16 +1660,16 @@
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -1670,31 +1677,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -1702,13 +1709,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>28</v>
@@ -1717,16 +1724,16 @@
         <v>57</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -1734,13 +1741,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1749,16 +1756,16 @@
         <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -1766,13 +1773,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>27</v>
@@ -1781,16 +1788,16 @@
         <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
@@ -1798,31 +1805,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -1830,13 +1837,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
@@ -1845,16 +1852,16 @@
         <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1862,31 +1869,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -1894,31 +1901,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -1926,31 +1933,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1958,31 +1965,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18">
@@ -1990,31 +1997,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19">
@@ -2022,31 +2029,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
@@ -2054,31 +2061,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21">
@@ -2086,31 +2093,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22">
@@ -2118,31 +2125,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23">
@@ -2150,31 +2157,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -2182,31 +2189,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25">
@@ -2214,31 +2221,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26">
@@ -2246,31 +2253,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2323,48 +2330,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
@@ -2373,54 +2380,54 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K3" s="3">
         <v>8</v>
@@ -2428,118 +2435,118 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
         <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
@@ -2548,68 +2555,68 @@
         <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="K7" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K8" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>28</v>
@@ -2618,33 +2625,33 @@
         <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K9" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2653,33 +2660,33 @@
         <v>54</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
@@ -2688,68 +2695,68 @@
         <v>52</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K11" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K12" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
@@ -2758,54 +2765,54 @@
         <v>47</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K13" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -2813,699 +2820,699 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="K15" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K16" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="K17" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="K18" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="K20" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="K21" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="K22" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="K23" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K24" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="K26" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>56</v>
+        <v>170</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K27" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>161</v>
+        <v>49</v>
       </c>
       <c r="K28" s="3">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>84</v>
+        <v>178</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>86</v>
+        <v>180</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="K29" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="K30" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E31" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="K31" s="3">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K32" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E34" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K34" s="3">
         <v>8</v>
@@ -3513,363 +3520,363 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>191</v>
+        <v>58</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>65</v>
+        <v>206</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="K36" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="K37" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="K38" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E39" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c r="K39" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K40" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>215</v>
+        <v>62</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>91</v>
+        <v>225</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="K41" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>189</v>
+        <v>62</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K42" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="K43" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>225</v>
+        <v>70</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>70</v>
+        <v>237</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>229</v>
+        <v>76</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3878,33 +3885,33 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K45" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>103</v>
+        <v>240</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>232</v>
+        <v>112</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3913,208 +3920,208 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K46" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>86</v>
+        <v>246</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K47" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E48" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="K48" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>67</v>
+        <v>255</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="K49" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K50" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>65</v>
+        <v>262</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>67</v>
+        <v>264</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>53</v>
+        <v>267</v>
       </c>
       <c r="K51" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>253</v>
+        <v>76</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4123,19 +4130,19 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K52" s="3">
         <v>8</v>
@@ -4143,13 +4150,13 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>256</v>
+        <v>131</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>258</v>
+        <v>81</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4158,33 +4165,33 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>261</v>
+        <v>183</v>
       </c>
       <c r="K53" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>264</v>
+        <v>76</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4193,33 +4200,33 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>165</v>
+        <v>67</v>
       </c>
       <c r="K54" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4228,33 +4235,33 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>70</v>
+        <v>183</v>
       </c>
       <c r="K55" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>67</v>
+        <v>284</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4263,138 +4270,138 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K56" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E57" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>53</v>
+        <v>237</v>
       </c>
       <c r="K57" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E58" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>282</v>
+        <v>187</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E59" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="K59" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>286</v>
+        <v>214</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>253</v>
+        <v>297</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>26</v>
@@ -4403,33 +4410,33 @@
         <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="K60" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>67</v>
+        <v>301</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>26</v>
@@ -4438,33 +4445,33 @@
         <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K61" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>202</v>
+        <v>286</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>295</v>
+        <v>76</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>26</v>
@@ -4473,19 +4480,19 @@
         <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="K62" s="3">
         <v>5</v>
@@ -4493,118 +4500,118 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>297</v>
+        <v>44</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>299</v>
+        <v>255</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K63" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E64" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="K64" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>285</v>
+        <v>118</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E65" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>289</v>
+        <v>55</v>
       </c>
       <c r="K65" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>286</v>
+        <v>314</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>253</v>
+        <v>159</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
@@ -4613,33 +4620,33 @@
         <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K66" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>309</v>
+        <v>62</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>86</v>
+        <v>317</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
@@ -4648,33 +4655,33 @@
         <v>3</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="K67" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>313</v>
+        <v>62</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>315</v>
+        <v>112</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4683,33 +4690,33 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K68" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>317</v>
+        <v>62</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>319</v>
+        <v>76</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4718,33 +4725,33 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>261</v>
+        <v>73</v>
       </c>
       <c r="K69" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4753,33 +4760,33 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>53</v>
+        <v>267</v>
       </c>
       <c r="K70" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>325</v>
+        <v>76</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4788,54 +4795,52 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="K71" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>103</v>
+        <v>329</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>327</v>
+        <v>196</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E72" s="3">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>287</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K72" s="3">
         <v>8</v>
@@ -4843,144 +4848,39 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>103</v>
+        <v>331</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>67</v>
+        <v>333</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E73" s="3">
-        <v>3</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>292</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K73" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E74" s="3">
-        <v>3</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K74" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E75" s="3">
-        <v>3</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E76" s="3">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="K76" s="3">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K76"/>
+  <autoFilter ref="A1:K73"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -5054,9 +4954,6 @@
     <hyperlink ref="I71" r:id="rId70"/>
     <hyperlink ref="I72" r:id="rId71"/>
     <hyperlink ref="I73" r:id="rId72"/>
-    <hyperlink ref="I74" r:id="rId73"/>
-    <hyperlink ref="I75" r:id="rId74"/>
-    <hyperlink ref="I76" r:id="rId75"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5064,9 +4961,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -5075,328 +4972,234 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>107</v>
+        <v>213</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>181</v>
+        <v>62</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>182</v>
+        <v>227</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>189</v>
+        <v>282</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>190</v>
+        <v>283</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>193</v>
+        <v>285</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>187</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>194</v>
+        <v>294</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>195</v>
+        <v>288</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>196</v>
+        <v>296</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>202</v>
+        <v>331</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>224</v>
+        <v>332</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3">
-        <v>12</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>213</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>226</v>
+        <v>334</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="3">
-        <v>6</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="3">
-        <v>6</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="3">
-        <v>3</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="3">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5407,10 +5210,6 @@
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
     <hyperlink ref="F10" r:id="rId9"/>
-    <hyperlink ref="F11" r:id="rId10"/>
-    <hyperlink ref="F12" r:id="rId11"/>
-    <hyperlink ref="F13" r:id="rId12"/>
-    <hyperlink ref="F14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5425,79 +5224,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B2" s="3">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>213</v>
+        <v>341</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>344</v>
+        <v>198</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B7" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8">
@@ -5505,98 +5304,98 @@
         <v>292</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>311</v>
+        <v>231</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>300</v>
+        <v>228</v>
       </c>
       <c r="B10" s="3">
         <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>352</v>
+        <v>302</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -5613,13 +5412,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
@@ -5627,10 +5426,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3">
@@ -5638,10 +5437,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4">
@@ -5649,10 +5448,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5">
@@ -5660,10 +5459,21 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>369</v>
+      <c r="C6" s="3" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -5681,51 +5491,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W23.xlsx
+++ b/reports/devops-juniors-israel-2026-W23.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-02T10:54:26</t>
+    <t xml:space="preserve">2026-06-03T11:22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -202,6 +202,21 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
@@ -235,9 +250,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automation student- Jerusalem</t>
   </si>
   <si>
@@ -307,6 +319,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
   </si>
   <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
@@ -322,6 +349,21 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
   </si>
   <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
@@ -337,754 +379,712 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
   </si>
   <si>
     <t xml:space="preserve">Bria AI</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
   </si>
   <si>
-    <t xml:space="preserve">Global Service Desk Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/global-service-desk-representative-at-radware-4407743786</t>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4418390308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Augury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Eng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ultra Information Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-eng-at-ultra-information-solutions-4412395476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4422886760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">morning by Green Invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-morning-by-green-invoice-4368658163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intezer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peax dorcom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-peax-dorcom-4419663768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varonis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-engineer-at-varonis-4389733678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elspec Engineering ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4419242661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-unilink-ltd-4419138857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
   </si>
   <si>
     <t xml:space="preserve">Information Technology Help Desk</t>
   </si>
   <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-proteantecs-4417085243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zensar Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-at-zensar-technologies-4418821535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artivion EMEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Databases, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-engineer-at-artivion-emea-4423879474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7055205?gh_jid=7055205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4418390308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plarium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4422886760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-plaee-4421385634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הכוורת CRM- תוכנה לניהול חכם - TheBee CRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-at-%D7%94%D7%9B%D7%95%D7%95%D7%A8%D7%AA-crm-%D7%AA%D7%95%D7%9B%D7%A0%D7%94-%D7%9C%D7%A0%D7%99%D7%94%D7%95%D7%9C-%D7%97%D7%9B%D7%9D-thebee-crm-4416812064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futuros Profesionales Trainee AutomatizaciÃ³n de Procesos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universia Argentina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buenos Aires y alrededores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-futuros-profesionales-trainee-automatizacion-de-procesos-universia-argentina-1132661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-sela-4418758138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk JB-594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-jb-594-at-pwc-israel-4410017501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-confidential-4418731915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT HelpDesk Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAST Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-admin-at-vast-data-4401197444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Representative (Full-Time, On-Site | Be’er Sheva – Gav Yam Park)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SITE123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-full-time-on-site-be%E2%80%99er-sheva-%E2%80%93-gav-yam-park-at-site123-4419228442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4419242661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-unilink-ltd-4419138857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sderot, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4416075873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-spinomenal-4369538005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fireberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fireberry-4415491964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-south-apac-sea-anz-ind-subcont-4418372549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futuros Profesionales Trainee AutomatizaciÃ³n de Procesos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universia Argentina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buenos Aires y alrededores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-futuros-profesionales-trainee-automatizacion-de-procesos-universia-argentina-1132661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">Kubernetes</t>
@@ -1262,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1270,7 +1270,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1278,7 +1278,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -1368,7 +1368,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1376,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1410,7 +1410,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
@@ -1418,7 +1418,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -1587,25 +1587,25 @@
         <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="3">
-        <v>88</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1613,31 +1613,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>88</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3">
-        <v>74</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1645,31 +1645,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
@@ -1677,31 +1677,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="3">
+        <v>70</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3">
-        <v>64</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -1709,19 +1709,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>86</v>
@@ -1733,7 +1733,7 @@
         <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -1741,31 +1741,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F10" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -1773,31 +1773,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3">
+        <v>54</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="3">
-        <v>52</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="12">
@@ -1805,31 +1805,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3">
+        <v>52</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>47</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -1837,31 +1837,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3">
+        <v>52</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>47</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -1869,31 +1869,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>109</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1901,31 +1901,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -1933,28 +1933,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>49</v>
@@ -1965,31 +1965,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1997,31 +1997,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -2029,31 +2029,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20">
@@ -2061,31 +2061,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
@@ -2093,31 +2093,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22">
@@ -2125,31 +2125,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23">
@@ -2157,31 +2157,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
@@ -2189,31 +2189,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
@@ -2221,31 +2221,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26">
@@ -2253,19 +2253,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>62</v>
+        <v>159</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>160</v>
@@ -2277,7 +2277,7 @@
         <v>161</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2317,7 +2317,7 @@
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2395,7 +2395,7 @@
         <v>49</v>
       </c>
       <c r="K2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -2430,7 +2430,7 @@
         <v>55</v>
       </c>
       <c r="K3" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2465,7 +2465,7 @@
         <v>61</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -2476,153 +2476,153 @@
         <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="3">
+        <v>100</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3">
-        <v>88</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="K5" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>88</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3">
-        <v>74</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="K6" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K7" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3">
+        <v>70</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3">
-        <v>64</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>86</v>
@@ -2637,30 +2637,30 @@
         <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K9" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E10" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>167</v>
@@ -2669,135 +2669,135 @@
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="K10" s="3">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>54</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="3">
-        <v>52</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="K11" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3">
+        <v>52</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>47</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="K12" s="3">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3">
+        <v>52</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>47</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K13" s="3">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>109</v>
@@ -2806,36 +2806,36 @@
         <v>167</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>167</v>
@@ -2844,33 +2844,33 @@
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="K15" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>167</v>
@@ -2879,33 +2879,33 @@
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>49</v>
       </c>
       <c r="K16" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>167</v>
@@ -2914,33 +2914,33 @@
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="K17" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>167</v>
@@ -2949,33 +2949,33 @@
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="K18" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>167</v>
@@ -2984,33 +2984,33 @@
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K19" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>167</v>
@@ -3019,33 +3019,33 @@
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="K20" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>167</v>
@@ -3054,33 +3054,33 @@
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K21" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>167</v>
@@ -3089,33 +3089,33 @@
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K22" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>167</v>
@@ -3124,33 +3124,33 @@
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="K23" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>167</v>
@@ -3159,10 +3159,10 @@
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -3170,22 +3170,22 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>167</v>
@@ -3194,30 +3194,30 @@
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="K25" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>62</v>
+        <v>159</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>160</v>
@@ -3232,126 +3232,126 @@
         <v>161</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="K26" s="3">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>23</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="3">
-        <v>20</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K27" s="3">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>23</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>20</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="K28" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>20</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E29" s="3">
-        <v>17</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="K29" s="3">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3360,7 +3360,7 @@
         <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>167</v>
@@ -3369,68 +3369,68 @@
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="K30" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>17</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" s="3">
-        <v>16</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="K31" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>17</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="3">
-        <v>16</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>167</v>
@@ -3445,7 +3445,7 @@
         <v>49</v>
       </c>
       <c r="K32" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
@@ -3456,51 +3456,51 @@
         <v>196</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="3">
+        <v>16</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="3">
-        <v>13</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="K33" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>94</v>
+        <v>201</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>167</v>
@@ -3509,33 +3509,33 @@
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K34" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E35" s="3">
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>167</v>
@@ -3544,24 +3544,24 @@
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K35" s="3">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3570,7 +3570,7 @@
         <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>167</v>
@@ -3579,24 +3579,24 @@
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K36" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
@@ -3605,7 +3605,7 @@
         <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>167</v>
@@ -3614,24 +3614,24 @@
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="K37" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>213</v>
+        <v>67</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3640,7 +3640,7 @@
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>167</v>
@@ -3649,33 +3649,33 @@
         <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K38" s="3">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>218</v>
+        <v>123</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>167</v>
@@ -3687,53 +3687,53 @@
         <v>219</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="K39" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="3">
+        <v>12</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="3">
-        <v>10</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="K40" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>62</v>
+        <v>223</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>225</v>
@@ -3745,7 +3745,7 @@
         <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>167</v>
@@ -3754,24 +3754,24 @@
         <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K41" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>81</v>
+        <v>228</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3780,33 +3780,33 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>167</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>229</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>230</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3827,21 +3827,21 @@
         <v>232</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="K43" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="C44" s="3" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3850,33 +3850,33 @@
         <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="K44" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>97</v>
+        <v>236</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3885,7 +3885,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>167</v>
@@ -3894,24 +3894,24 @@
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K45" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>240</v>
+        <v>106</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3920,7 +3920,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>167</v>
@@ -3929,45 +3929,45 @@
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K46" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="D47" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="3">
+        <v>10</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" s="3">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="J47" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="K47" s="3">
         <v>9</v>
@@ -3975,13 +3975,13 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>26</v>
@@ -3990,7 +3990,7 @@
         <v>8</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>167</v>
@@ -3999,59 +3999,59 @@
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K48" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="D49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="3">
-        <v>6</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="J49" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K49" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>206</v>
+        <v>255</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4060,33 +4060,33 @@
         <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>167</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K50" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4095,33 +4095,33 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="J51" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="G51" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>267</v>
-      </c>
       <c r="K51" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4130,19 +4130,19 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="J52" s="3" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="K52" s="3">
         <v>8</v>
@@ -4150,13 +4150,13 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>131</v>
+        <v>271</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>272</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4177,10 +4177,10 @@
         <v>274</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -4191,7 +4191,7 @@
         <v>276</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>76</v>
+        <v>277</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4200,7 +4200,7 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>167</v>
@@ -4209,24 +4209,24 @@
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K54" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4235,7 +4235,7 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>167</v>
@@ -4247,21 +4247,21 @@
         <v>281</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>183</v>
+        <v>72</v>
       </c>
       <c r="K55" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>282</v>
+        <v>111</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>283</v>
+        <v>156</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>284</v>
+        <v>85</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4270,7 +4270,7 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>167</v>
@@ -4279,10 +4279,10 @@
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="K56" s="3">
         <v>0</v>
@@ -4290,57 +4290,57 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>286</v>
+        <v>211</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>167</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>237</v>
+        <v>66</v>
       </c>
       <c r="K57" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>292</v>
+        <v>249</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>167</v>
@@ -4349,24 +4349,24 @@
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="K58" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>187</v>
+        <v>289</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>295</v>
+        <v>257</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>26</v>
@@ -4375,33 +4375,33 @@
         <v>4</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>167</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>61</v>
+        <v>293</v>
       </c>
       <c r="K59" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>214</v>
+        <v>294</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>26</v>
@@ -4410,7 +4410,7 @@
         <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>167</v>
@@ -4419,24 +4419,24 @@
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>267</v>
+        <v>61</v>
       </c>
       <c r="K60" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>299</v>
+        <v>195</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>300</v>
+        <v>208</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>26</v>
@@ -4445,7 +4445,7 @@
         <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>167</v>
@@ -4454,24 +4454,24 @@
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="K61" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>76</v>
+        <v>301</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>26</v>
@@ -4480,7 +4480,7 @@
         <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>167</v>
@@ -4489,59 +4489,59 @@
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>237</v>
+        <v>66</v>
       </c>
       <c r="K62" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>44</v>
+        <v>289</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>255</v>
+        <v>80</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E63" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>167</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>73</v>
+        <v>293</v>
       </c>
       <c r="K63" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4550,33 +4550,33 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>167</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K64" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>118</v>
+        <v>307</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
@@ -4585,33 +4585,33 @@
         <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>313</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>55</v>
       </c>
       <c r="K65" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>131</v>
+        <v>311</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
@@ -4620,7 +4620,7 @@
         <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>167</v>
@@ -4629,24 +4629,24 @@
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="K66" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>317</v>
+        <v>113</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
@@ -4655,7 +4655,7 @@
         <v>3</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>167</v>
@@ -4664,24 +4664,24 @@
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K67" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>62</v>
+        <v>317</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>25</v>
@@ -4690,7 +4690,7 @@
         <v>3</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>167</v>
@@ -4702,21 +4702,21 @@
         <v>320</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>73</v>
+        <v>265</v>
       </c>
       <c r="K68" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>62</v>
+        <v>321</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>25</v>
@@ -4725,7 +4725,7 @@
         <v>3</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>167</v>
@@ -4734,24 +4734,24 @@
         <v>31</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>73</v>
+        <v>185</v>
       </c>
       <c r="K69" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>323</v>
+        <v>44</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>325</v>
+        <v>80</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>25</v>
@@ -4760,7 +4760,7 @@
         <v>3</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>167</v>
@@ -4769,24 +4769,24 @@
         <v>31</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>267</v>
+        <v>55</v>
       </c>
       <c r="K70" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>44</v>
+        <v>325</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>25</v>
@@ -4795,7 +4795,7 @@
         <v>3</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>167</v>
@@ -4804,24 +4804,24 @@
         <v>31</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>183</v>
+        <v>105</v>
       </c>
       <c r="K71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>27</v>
@@ -4837,24 +4837,24 @@
         <v>31</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>55</v>
       </c>
       <c r="K72" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>332</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>333</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>27</v>
@@ -4870,13 +4870,13 @@
         <v>33</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>61</v>
       </c>
       <c r="K73" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4961,9 +4961,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="52" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4995,221 +4995,127 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>109</v>
+        <v>234</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>110</v>
+        <v>235</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>152</v>
+        <v>249</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>153</v>
+        <v>282</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>213</v>
+        <v>325</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>214</v>
+        <v>326</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>216</v>
+        <v>327</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5224,98 +5130,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B2" s="3">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B3" s="3">
+        <v>27</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="B3" s="3">
-        <v>29</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B4" s="3">
         <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B5" s="3">
         <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>310</v>
+        <v>231</v>
       </c>
       <c r="B6" s="3">
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>292</v>
+        <v>345</v>
       </c>
       <c r="B8" s="3">
         <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>231</v>
+        <v>347</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>348</v>
@@ -5323,10 +5229,10 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>349</v>
@@ -5334,21 +5240,21 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>351</v>
+        <v>313</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>352</v>
@@ -5359,7 +5265,7 @@
         <v>353</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>354</v>
@@ -5370,7 +5276,7 @@
         <v>355</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>356</v>
@@ -5381,7 +5287,7 @@
         <v>357</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>358</v>
@@ -5392,7 +5298,7 @@
         <v>359</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>360</v>
@@ -5437,7 +5343,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>364</v>
@@ -5448,7 +5354,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>365</v>
@@ -5508,7 +5414,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>371</v>
@@ -5520,7 +5426,7 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>371</v>

--- a/reports/devops-juniors-israel-2026-W23.xlsx
+++ b/reports/devops-juniors-israel-2026-W23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-03T11:22:14</t>
+    <t xml:space="preserve">2026-06-04T10:12:08</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,18 +94,21 @@
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
     <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -202,739 +205,730 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4398384580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
   </si>
   <si>
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMware System Administrator (36310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-system-administrator-36310-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4421685538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4422405627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proteanTecs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-island-4408877123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riverside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reline IT Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4418390308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4422886760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plarium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Voyager Labs</t>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassesUSA.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP ECC System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT HelpDesk Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAST Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-admin-at-vast-data-4401197444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-intel-4424065569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4419242661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware System Administrator (36310)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-system-administrator-36310-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4421685538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortinet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, GCP, Cloud (any), Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-fortinet-4393535304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regatta Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-regatta-data-4366167298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bria AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-bria-ai-4420446496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Cloud (any), Databases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-extreme-4410984686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4418390308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior IT Support Technician-Temporary 10 Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-support-technician-temporary-10-months-at-augury-4418665913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Eng.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ultra Information Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-eng-at-ultra-information-solutions-4412395476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4422886760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">morning by Green Invoice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-morning-by-green-invoice-4368658163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intezer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-intezer-4417050672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-peax-dorcom-4419663768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Varonis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-engineer-at-varonis-4389733678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support – Power Quality Meters &amp; Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elspec Engineering ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-%E2%80%93-power-quality-meters-software-at-elspec-engineering-ltd-4413397801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4419242661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-unilink-ltd-4419138857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-specialist-at-unity-4419979615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
   </si>
   <si>
     <t xml:space="preserve">Information Technology Help Desk</t>
@@ -949,63 +943,30 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
   </si>
   <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oktopost</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Tier 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yavne, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plaee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-plaee-4421385634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/developer-support-engineer-at-unity-4417759260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">הכוורת CRM- תוכנה לניהול חכם - TheBee CRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-representative-at-%D7%94%D7%9B%D7%95%D7%95%D7%A8%D7%AA-crm-%D7%AA%D7%95%D7%9B%D7%A0%D7%94-%D7%9C%D7%A0%D7%99%D7%94%D7%95%D7%9C-%D7%97%D7%9B%D7%9D-thebee-crm-4416812064</t>
-  </si>
-  <si>
     <t xml:space="preserve">System Engineering Student</t>
   </si>
   <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
   </si>
   <si>
+    <t xml:space="preserve">Fresh Graduate Management Trainee Accounting Associate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliveree On-Demand Logistics (Southeast Asia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jakarta,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-fresh-graduate-management-trainee-accounting-associate-deliveree-on-demand-logistics-southeast-asia-1132811</t>
+  </si>
+  <si>
     <t xml:space="preserve">Futuros Profesionales Trainee AutomatizaciÃ³n de Procesos</t>
   </si>
   <si>
@@ -1042,19 +1003,25 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
@@ -1063,34 +1030,25 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -1108,16 +1066,19 @@
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
     <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1254,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -1262,7 +1223,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1270,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -1278,7 +1239,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -1360,7 +1321,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
@@ -1368,7 +1329,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1376,7 +1337,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -1396,29 +1357,29 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3">
-        <v>63</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
@@ -1426,7 +1387,15 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1450,34 +1419,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -1485,13 +1454,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>25</v>
@@ -1500,16 +1469,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -1517,13 +1486,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>29</v>
@@ -1532,16 +1501,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -1549,13 +1518,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>28</v>
@@ -1564,16 +1533,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1581,31 +1550,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -1613,31 +1582,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -1645,31 +1614,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -1677,31 +1646,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
         <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
@@ -1709,31 +1678,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="3">
         <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -1741,13 +1710,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>28</v>
@@ -1756,16 +1725,16 @@
         <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1773,13 +1742,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>25</v>
@@ -1788,16 +1757,16 @@
         <v>54</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
@@ -1805,31 +1774,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
         <v>52</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -1837,31 +1806,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" s="3">
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -1869,31 +1838,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1901,31 +1870,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
@@ -1933,7 +1902,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>117</v>
@@ -1951,13 +1920,13 @@
         <v>119</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1971,7 +1940,7 @@
         <v>122</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
@@ -1980,16 +1949,16 @@
         <v>44</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -1997,31 +1966,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="3">
+        <v>44</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>40</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -2029,13 +1998,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>25</v>
@@ -2044,16 +2013,16 @@
         <v>34</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="20">
@@ -2061,16 +2030,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F20" s="3">
         <v>32</v>
@@ -2079,13 +2048,13 @@
         <v>136</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21">
@@ -2093,31 +2062,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>30</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="3">
-        <v>32</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="22">
@@ -2131,25 +2100,25 @@
         <v>144</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>27</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3">
-        <v>30</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23">
@@ -2157,31 +2126,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="D23" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>149</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -2189,31 +2158,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="3">
+        <v>23</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>27</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25">
@@ -2221,31 +2190,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="3">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="3">
-        <v>26</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="26">
@@ -2253,31 +2222,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2316,8 +2285,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2330,48 +2299,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
@@ -2380,33 +2349,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -2415,33 +2384,33 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>28</v>
@@ -2450,208 +2419,208 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K5" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="3">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
         <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="K7" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
         <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K8" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3">
         <v>64</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>28</v>
@@ -2660,33 +2629,33 @@
         <v>57</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
@@ -2695,19 +2664,19 @@
         <v>54</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="K11" s="3">
         <v>3</v>
@@ -2715,147 +2684,147 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
         <v>52</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3">
         <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="K14" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E15" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="K15" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>117</v>
@@ -2873,19 +2842,19 @@
         <v>119</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K16" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -2896,7 +2865,7 @@
         <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
@@ -2905,68 +2874,68 @@
         <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="K17" s="3">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3">
+        <v>44</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>40</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="K18" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>25</v>
@@ -2975,36 +2944,36 @@
         <v>34</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="K19" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>62</v>
+        <v>134</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" s="3">
         <v>32</v>
@@ -3013,54 +2982,54 @@
         <v>136</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>137</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="K20" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>30</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="3">
-        <v>32</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="K21" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -3071,311 +3040,311 @@
         <v>144</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>27</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="3">
-        <v>30</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="K22" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="C23" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>149</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="K23" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>23</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="3">
-        <v>27</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3">
+        <v>23</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="3">
-        <v>26</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K25" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K26" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="K27" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>113</v>
+        <v>174</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="K28" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="K29" s="3">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E30" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="K30" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -3386,31 +3355,31 @@
         <v>187</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>189</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="K31" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -3424,28 +3393,28 @@
         <v>192</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>193</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>194</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="K32" s="3">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
@@ -3453,115 +3422,115 @@
         <v>195</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K33" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3">
+        <v>13</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="3">
-        <v>16</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K34" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K35" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3570,162 +3539,162 @@
         <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="K36" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="3">
+        <v>12</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>13</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="K37" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>67</v>
+        <v>212</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3">
+        <v>10</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="3">
-        <v>13</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="J38" s="3" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="K38" s="3">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>111</v>
+        <v>217</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>219</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="K39" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>220</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>10</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="3">
-        <v>12</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="G40" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>222</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="K40" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -3736,7 +3705,7 @@
         <v>224</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>225</v>
+        <v>71</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3745,33 +3714,33 @@
         <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I41" s="3" t="s">
+      <c r="J41" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K41" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>67</v>
+        <v>228</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3780,19 +3749,19 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K42" s="3">
         <v>10</v>
@@ -3800,13 +3769,13 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3815,243 +3784,243 @@
         <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>171</v>
+        <v>74</v>
       </c>
       <c r="K43" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>106</v>
+        <v>234</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="3">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E45" s="3">
-        <v>10</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="G45" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K45" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>106</v>
+        <v>243</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K46" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="K47" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E48" s="3">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K48" s="3">
         <v>8</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="K48" s="3">
-        <v>10</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>253</v>
+        <v>65</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="K49" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4060,33 +4029,33 @@
         <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="K50" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
@@ -4095,33 +4064,33 @@
         <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>265</v>
+        <v>74</v>
       </c>
       <c r="K51" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>267</v>
+        <v>148</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>268</v>
+        <v>87</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
@@ -4130,22 +4099,22 @@
         <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>270</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="K52" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4156,7 +4125,7 @@
         <v>272</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4165,22 +4134,22 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
+      <c r="J53" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="J53" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="K53" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -4191,7 +4160,7 @@
         <v>276</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4200,22 +4169,22 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>278</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="K54" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -4226,322 +4195,322 @@
         <v>280</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E55" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>72</v>
+        <v>227</v>
       </c>
       <c r="K55" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>156</v>
+        <v>284</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="K56" s="3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>283</v>
+        <v>100</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>284</v>
+        <v>101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E57" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K57" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>286</v>
+        <v>182</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E58" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>171</v>
+        <v>62</v>
       </c>
       <c r="K58" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E59" s="3">
         <v>4</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>293</v>
+        <v>74</v>
       </c>
       <c r="K59" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>195</v>
+        <v>45</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>295</v>
+        <v>245</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E60" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="K60" s="3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>195</v>
+        <v>298</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>208</v>
+        <v>299</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E61" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>265</v>
+        <v>157</v>
       </c>
       <c r="K61" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>301</v>
+        <v>130</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K62" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>293</v>
+        <v>56</v>
       </c>
       <c r="K63" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>257</v>
+        <v>65</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4550,337 +4519,125 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K64" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>308</v>
+        <v>191</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E65" s="3">
-        <v>3</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>309</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K65" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>69</v>
+        <v>315</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E66" s="3">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>313</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>171</v>
+        <v>68</v>
       </c>
       <c r="K66" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>143</v>
+        <v>317</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>113</v>
+        <v>319</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E67" s="3">
-        <v>3</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>291</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K67" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E68" s="3">
-        <v>3</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K68" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E69" s="3">
-        <v>3</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="K69" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K70" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="3">
-        <v>3</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="K71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K72" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E73" s="3">
-        <v>0</v>
-      </c>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="K73" s="3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K73"/>
+  <autoFilter ref="A1:K67"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4948,12 +4705,6 @@
     <hyperlink ref="I65" r:id="rId64"/>
     <hyperlink ref="I66" r:id="rId65"/>
     <hyperlink ref="I67" r:id="rId66"/>
-    <hyperlink ref="I68" r:id="rId67"/>
-    <hyperlink ref="I69" r:id="rId68"/>
-    <hyperlink ref="I70" r:id="rId69"/>
-    <hyperlink ref="I71" r:id="rId70"/>
-    <hyperlink ref="I72" r:id="rId71"/>
-    <hyperlink ref="I73" r:id="rId72"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4961,9 +4712,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4972,150 +4723,196 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>233</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>234</v>
+        <v>115</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>235</v>
+        <v>116</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>249</v>
+        <v>175</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>282</v>
+        <v>176</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>325</v>
+        <v>287</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>326</v>
+        <v>100</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
         <v>3</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>105</v>
+      <c r="E7" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5130,178 +4927,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B2" s="3">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>345</v>
+        <v>193</v>
       </c>
       <c r="B8" s="3">
         <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="B9" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="B10" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>353</v>
+        <v>301</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5318,13 +5115,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2">
@@ -5332,10 +5129,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3">
@@ -5343,10 +5140,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4">
@@ -5354,10 +5151,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5">
@@ -5368,7 +5165,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6">
@@ -5379,7 +5176,18 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>367</v>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -5397,51 +5205,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W23.xlsx
+++ b/reports/devops-juniors-israel-2026-W23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="328">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-04T10:12:08</t>
+    <t xml:space="preserve">2026-06-05T10:10:26</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,18 +94,18 @@
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
+    <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
@@ -187,832 +187,763 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior AI SRE Developer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helfy</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-ai-sre-developer-at-helfy-4413461829</t>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Git, Terraform/IaC, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/production-support-engineer-at-extreme-4418657999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-codevalue-4421843930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristocrat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modellama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-modellama-4361100331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Island</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-island-4408877123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4410129423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategy Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer IM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4422886760</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bright Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlassesUSA.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician - junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk - 239819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excis Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shoham, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT HelpDesk Admin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAST Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-admin-at-vast-data-4401197444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist (Part time )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-intel-4424065569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4419242661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4398384580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4417872616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VMware System Administrator (36310)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vmware-system-administrator-36310-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4421685538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-cato-networks-4398801612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iFOR FINTECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4422405627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteanTecs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-proteantecs-4373568445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-island-4408877123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riverside</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-riverside-4409620033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strategy Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reline IT Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nes Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-reline-it-solutions-4418390308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4422886760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plarium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-administrator-at-plarium-4402847792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brazil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh Graduate Management Trainee Accounting Associate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deliveree On-Demand Logistics (Southeast Asia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jakarta,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-fresh-graduate-management-trainee-accounting-associate-deliveree-on-demand-logistics-southeast-asia-1132811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bright Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-at-bright-data-4419013320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GlassesUSA.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beth-El Industries Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP ECC System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sap-ecc-system-administrator-at-sisl-global-4409153565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/5999705004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician - junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-junior-at-mornex-4416807351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk - 239819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Ayish, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excis Compliance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shoham, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist (Part time )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-part-time-at-nuvei-4421067573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT HelpDesk Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAST Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-admin-at-vast-data-4401197444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unity3D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-intel-4424065569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4419242661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M.D. Mechanical Devices Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-m-d-mechanical-devices-ltd-4420118096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresh Graduate Management Trainee Accounting Associate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deliveree On-Demand Logistics (Southeast Asia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jakarta,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-fresh-graduate-management-trainee-accounting-associate-deliveree-on-demand-logistics-southeast-asia-1132811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futuros Profesionales Trainee AutomatizaciÃ³n de Procesos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universia Argentina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buenos Aires y alrededores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-futuros-profesionales-trainee-automatizacion-de-procesos-universia-argentina-1132661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -1021,34 +952,10 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -1066,16 +973,16 @@
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
@@ -1215,7 +1122,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -1223,7 +1130,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1231,7 +1138,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -1239,7 +1146,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -1321,7 +1228,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
@@ -1329,7 +1236,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1337,7 +1244,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -1345,7 +1252,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1379,7 +1286,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30">
@@ -1395,7 +1302,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1407,7 +1314,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1495,7 +1402,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1527,7 +1434,7 @@
         <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1562,7 +1469,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>66</v>
@@ -1591,7 +1498,7 @@
         <v>71</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
         <v>74</v>
@@ -1606,7 +1513,7 @@
         <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -1614,31 +1521,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="3">
+        <v>70</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>74</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -1646,31 +1553,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3">
+        <v>64</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3">
-        <v>70</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -1678,31 +1585,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>60</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="3">
-        <v>64</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -1716,10 +1623,10 @@
         <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" s="3">
         <v>57</v>
@@ -1751,10 +1658,10 @@
         <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>97</v>
@@ -1766,7 +1673,7 @@
         <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -1780,25 +1687,25 @@
         <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>51</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3">
-        <v>52</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -1806,19 +1713,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>106</v>
@@ -1838,31 +1745,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -1870,31 +1777,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
+        <v>44</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="16">
@@ -1902,31 +1809,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
@@ -1934,31 +1841,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
@@ -1966,31 +1873,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -1998,31 +1905,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2030,31 +1937,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3">
         <v>27</v>
       </c>
-      <c r="F20" s="3">
-        <v>32</v>
-      </c>
       <c r="G20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -2062,31 +1969,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
@@ -2094,31 +2001,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -2126,19 +2033,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>148</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>149</v>
@@ -2150,7 +2057,7 @@
         <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24">
@@ -2158,13 +2065,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
@@ -2173,16 +2080,16 @@
         <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -2190,31 +2097,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>157</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -2222,31 +2129,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2299,7 +2206,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2314,22 +2221,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2">
@@ -2352,7 +2259,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>33</v>
@@ -2364,7 +2271,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -2378,7 +2285,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2387,7 +2294,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2399,7 +2306,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2413,7 +2320,7 @@
         <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2422,7 +2329,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2434,7 +2341,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -2451,13 +2358,13 @@
         <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2483,7 +2390,7 @@
         <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
         <v>74</v>
@@ -2492,7 +2399,7 @@
         <v>72</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2501,115 +2408,115 @@
         <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="K6" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3">
+        <v>70</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>74</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="K7" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3">
+        <v>64</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3">
-        <v>70</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K8" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3">
+        <v>60</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="3">
-        <v>64</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K9" s="3">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -2620,10 +2527,10 @@
         <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3">
         <v>57</v>
@@ -2632,7 +2539,7 @@
         <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2644,7 +2551,7 @@
         <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -2658,16 +2565,16 @@
         <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2676,10 +2583,10 @@
         <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="K11" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -2690,54 +2597,54 @@
         <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>51</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="3">
-        <v>52</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K12" s="3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E13" s="3">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2754,340 +2661,340 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
+        <v>44</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="K16" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K17" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="K18" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="K19" s="3">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3">
         <v>27</v>
       </c>
-      <c r="E20" s="3">
-        <v>32</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="K20" s="3">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="K21" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="K22" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>148</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>149</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
@@ -3096,21 +3003,21 @@
         <v>150</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="K23" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
@@ -3119,299 +3026,299 @@
         <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="K24" s="3">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>157</v>
+        <v>50</v>
       </c>
       <c r="K25" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="K26" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="K27" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="K29" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E30" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="K30" s="3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>50</v>
+        <v>191</v>
       </c>
       <c r="K31" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>192</v>
+        <v>59</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
         <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="K32" s="3">
         <v>11</v>
@@ -3419,1225 +3326,842 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>101</v>
+        <v>197</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
       <c r="K33" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>59</v>
+        <v>202</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K34" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>96</v>
+        <v>206</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>203</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K35" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="K36" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="K37" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="K38" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>74</v>
+        <v>227</v>
       </c>
       <c r="K39" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>87</v>
+        <v>230</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="3">
+        <v>6</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="K40" s="3">
         <v>10</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="K40" s="3">
-        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>71</v>
+        <v>236</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="K41" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>56</v>
       </c>
       <c r="K42" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>232</v>
+        <v>142</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="K43" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>236</v>
+        <v>76</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>74</v>
+        <v>199</v>
       </c>
       <c r="K44" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>74</v>
+        <v>252</v>
       </c>
       <c r="K45" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E46" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="K46" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>197</v>
+        <v>257</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>249</v>
+        <v>76</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E47" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="K47" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>253</v>
+        <v>95</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>254</v>
+        <v>96</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>255</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>257</v>
+        <v>108</v>
       </c>
       <c r="K48" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>243</v>
+        <v>172</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E49" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>142</v>
+        <v>191</v>
       </c>
       <c r="K49" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E50" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="K50" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>265</v>
+        <v>45</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="K51" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>148</v>
+        <v>272</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>87</v>
+        <v>273</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>108</v>
+        <v>233</v>
       </c>
       <c r="K52" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>274</v>
+        <v>56</v>
       </c>
       <c r="K53" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>275</v>
+        <v>99</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="K54" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>280</v>
+        <v>181</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>245</v>
+        <v>96</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E55" s="3">
-        <v>4</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>281</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>227</v>
+        <v>56</v>
       </c>
       <c r="K55" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E56" s="3">
-        <v>4</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>285</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="K56" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E57" s="3">
-        <v>4</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E58" s="3">
-        <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K58" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E59" s="3">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K59" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E60" s="3">
-        <v>3</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K60" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E61" s="3">
-        <v>3</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="K61" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" s="3">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="3">
-        <v>3</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K63" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E64" s="3">
-        <v>3</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K64" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" s="3">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K65" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E66" s="3">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67" s="3">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K67" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K67"/>
+  <autoFilter ref="A1:K56"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4694,17 +4218,6 @@
     <hyperlink ref="I54" r:id="rId53"/>
     <hyperlink ref="I55" r:id="rId54"/>
     <hyperlink ref="I56" r:id="rId55"/>
-    <hyperlink ref="I57" r:id="rId56"/>
-    <hyperlink ref="I58" r:id="rId57"/>
-    <hyperlink ref="I59" r:id="rId58"/>
-    <hyperlink ref="I60" r:id="rId59"/>
-    <hyperlink ref="I61" r:id="rId60"/>
-    <hyperlink ref="I62" r:id="rId61"/>
-    <hyperlink ref="I63" r:id="rId62"/>
-    <hyperlink ref="I64" r:id="rId63"/>
-    <hyperlink ref="I65" r:id="rId64"/>
-    <hyperlink ref="I66" r:id="rId65"/>
-    <hyperlink ref="I67" r:id="rId66"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4712,9 +4225,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="29" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4735,10 +4248,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -4755,7 +4268,7 @@
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>66</v>
@@ -4769,22 +4282,22 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>68</v>
@@ -4792,22 +4305,22 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>68</v>
@@ -4815,22 +4328,22 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>119</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="3">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>68</v>
@@ -4838,22 +4351,22 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>287</v>
+        <v>124</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="3">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>281</v>
+        <v>126</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>288</v>
+        <v>127</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>68</v>
@@ -4861,50 +4374,29 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>269</v>
+        <v>119</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>303</v>
+        <v>133</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>281</v>
+        <v>134</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>304</v>
+        <v>135</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G7"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -4912,7 +4404,6 @@
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4927,178 +4418,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>322</v>
+        <v>290</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>323</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="B2" s="3">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>324</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>325</v>
+        <v>293</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>327</v>
+        <v>183</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>221</v>
+        <v>298</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>307</v>
+        <v>259</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>331</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>193</v>
+        <v>301</v>
       </c>
       <c r="B8" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>332</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>333</v>
+        <v>278</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>334</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>335</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>336</v>
+        <v>274</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>339</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>340</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>342</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>344</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>346</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -5118,10 +4609,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>347</v>
+        <v>316</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>348</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2">
@@ -5129,10 +4620,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>349</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3">
@@ -5140,10 +4631,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4">
@@ -5151,10 +4642,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5">
@@ -5162,10 +4653,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>352</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6">
@@ -5176,7 +4667,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7">
@@ -5187,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>354</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -5208,13 +4699,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2">
@@ -5225,7 +4716,7 @@
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5234,10 +4725,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -5246,10 +4737,10 @@
         <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W23.xlsx
+++ b/reports/devops-juniors-israel-2026-W23.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="296">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-05T10:10:26</t>
+    <t xml:space="preserve">2026-06-07T09:32:03</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,21 +94,18 @@
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -187,301 +184,256 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4398384580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRS RADA Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation student- Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced IT System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iFOR FINTECH</t>
   </si>
   <si>
     <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beer Yaakov, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Virtualization, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABsystem-engineer-at-jobsseek-4415191565</t>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/experienced-it-system-administrator-at-ifor-fintech-4419287305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aidoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-05</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRS RADA Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-student-at-drs-rada-technologies-4399886674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation student- Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-jerusalem-at-radware-4412821363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Docker, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-support-engineer-level-1132895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4416620227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innoviz Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allied Worldwide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Bootcamp Course 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Git, Terraform/IaC, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/production-support-engineer-at-extreme-4418657999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux HPC Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben-Gurion University of the Negev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Be'er Sheva, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Kubernetes, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-ben-gurion-university-of-the-negev-4412773313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Window infrastructure &amp; DevOps Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), CI/CD, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/window-infrastructure-devops-student-at-intel-4402131061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aidoc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Git, Terraform/IaC, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-aidoc-4423356724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Engineer – Digital &amp; Applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-engineer-%E2%80%93-digital-applications-at-maytronics-4424048965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist - Temporary position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cato Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-cato-networks-4394155925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeValue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-codevalue-4421843930</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aristocrat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-aristocrat-4413900417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innoviz Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-innoviz-technologies-4407119527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modellama</t>
+    <t xml:space="preserve">CI/CD, Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (24892)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4410129423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
   </si>
   <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Active Directory, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-modellama-4361100331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Desktop Support Engineer (Freelance / Backfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allied Worldwide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-desktop-support-engineer-freelance-backfill-at-allied-worldwide-4423894444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Bootcamp Course 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-bootcamp-course-2-at-abra-4383549364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Island</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-island-4408877123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (24892)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-24892-at-yael-group-4410129423</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-qb-systems-ltd-4418941372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
   </si>
   <si>
     <t xml:space="preserve">IT Service Desk Specialist</t>
@@ -514,6 +466,57 @@
     <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4854356101?gh_jid=4854356101</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2E Solutions IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4406043821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4422886760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -532,90 +535,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2E Solutions IL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-e2e-solutions-il-4422575084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer IM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-im-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (IT Support Specialist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-it-support-specialist-at-unilink-ltd-4422886760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-evoke-4418935839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4418381305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -640,6 +559,15 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4841210101</t>
   </si>
   <si>
+    <t xml:space="preserve">Partner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-partner-4415284885</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Helpdesk Specialist</t>
   </si>
   <si>
@@ -667,6 +595,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-glassesusa-com-4400413150</t>
   </si>
   <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – WMS | עולם הלוגיסטיקה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beth-El Industries Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zikhron Yaakov, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-wms-%D7%A2%D7%95%D7%9C%D7%9D-%D7%94%D7%9C%D7%95%D7%92%D7%99%D7%A1%D7%98%D7%99%D7%A7%D7%94-at-beth-el-industries-ltd-4353742304</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Helpdesk</t>
   </si>
   <si>
@@ -715,7 +664,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-239819-at-experis-israel-4415278349</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-26</t>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
   </si>
   <si>
     <t xml:space="preserve">L2 Desktop Support Engineer - IL</t>
@@ -730,39 +694,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/l2-desktop-support-engineer-il-at-excis-compliance-4413448976</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk- Parental Leave Replacement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-parental-leave-replacement-at-pagaya-4418669487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-abra-4423876931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT HelpDesk Admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAST Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-admin-at-vast-data-4401197444</t>
-  </si>
-  <si>
     <t xml:space="preserve">IT Specialist (Part time )</t>
   </si>
   <si>
@@ -787,150 +718,132 @@
     <t xml:space="preserve">https://unity.com/careers/positions/7860478?gh_jid=7860478</t>
   </si>
   <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
+    <t xml:space="preserve">System Engineer- 2084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yavne, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-at-gness-4418548846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">לחברת ביטוח צומחת במרכז דרוש/ה HELPDESK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taldor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%9C%D7%97%D7%91%D7%A8%D7%AA-%D7%91%D7%99%D7%98%D7%95%D7%97-%D7%A6%D7%95%D7%9E%D7%97%D7%AA-%D7%91%D7%9E%D7%A8%D7%9B%D7%96-%D7%93%D7%A8%D7%95%D7%A9-%D7%94-helpdesk-at-taldor-4425008649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4412658786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-intel-4424065569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-sqlink-group-4419242661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer- 2084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-2084-at-tsg-4413409224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unity.com/careers/positions/7543658?gh_jid=7543658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NeoTech Israel | ניאוטק ישראל</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-help-desk-at-neotech-israel-%D7%A0%D7%99%D7%90%D7%95%D7%98%D7%A7-%D7%99%D7%A9%D7%A8%D7%90%D7%9C-4414860456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4418647779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresh Graduate Management Trainee Accounting Associate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deliveree On-Demand Logistics (Southeast Asia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jakarta,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-fresh-graduate-management-trainee-accounting-associate-deliveree-on-demand-logistics-southeast-asia-1132811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
@@ -946,16 +859,10 @@
     <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -973,19 +880,16 @@
     <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1122,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -1130,7 +1034,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1138,7 +1042,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1146,7 +1050,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -1228,7 +1132,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
@@ -1236,7 +1140,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -1244,7 +1148,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1264,29 +1168,29 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3"/>
       <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3"/>
+      <c r="B28" s="3">
+        <v>37</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1294,14 +1198,6 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1314,7 +1210,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1326,34 +1222,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -1361,13 +1257,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>25</v>
@@ -1376,16 +1272,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -1393,13 +1289,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>28</v>
@@ -1408,16 +1304,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -1425,31 +1321,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1457,31 +1353,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -1489,31 +1385,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3">
+        <v>70</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3">
-        <v>74</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -1521,31 +1417,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="3">
+        <v>57</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="3">
-        <v>70</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
@@ -1553,31 +1449,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3">
+        <v>52</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="3">
-        <v>64</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -1585,31 +1481,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="3">
+        <v>52</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3">
-        <v>60</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1617,31 +1513,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3">
+        <v>51</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="3">
-        <v>57</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1649,31 +1545,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3">
+        <v>47</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="3">
-        <v>52</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -1681,31 +1577,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>101</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -1722,16 +1618,16 @@
         <v>105</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>106</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>107</v>
@@ -1751,25 +1647,25 @@
         <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="3">
+        <v>32</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3">
-        <v>47</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -1777,31 +1673,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>30</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>44</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1815,25 +1711,25 @@
         <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>27</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>36</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -1841,31 +1737,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>126</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -1873,31 +1769,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
+        <v>24</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>30</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -1905,31 +1801,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>134</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -1937,31 +1833,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="3">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>27</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -1969,19 +1865,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>143</v>
@@ -1993,7 +1889,7 @@
         <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -2004,28 +1900,28 @@
         <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
@@ -2033,31 +1929,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24">
@@ -2065,31 +1961,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
@@ -2097,31 +1993,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>50</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26">
@@ -2129,31 +2025,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2192,8 +2088,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2206,48 +2102,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
@@ -2256,33 +2152,33 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K2" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>28</v>
@@ -2291,337 +2187,337 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="K3" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K4" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="K5" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3">
+        <v>70</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3">
-        <v>74</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K6" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="3">
+        <v>57</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3">
-        <v>70</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="K7" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3">
+        <v>52</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3">
-        <v>64</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3">
-        <v>60</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="K9" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="3">
-        <v>57</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K10" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>47</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="3">
-        <v>52</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="G11" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="K11" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="D12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -2635,19 +2531,19 @@
         <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>107</v>
@@ -2656,7 +2552,7 @@
         <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2667,66 +2563,66 @@
         <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="3">
+        <v>32</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="3">
-        <v>47</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K14" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>30</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>44</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K15" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2737,194 +2633,194 @@
         <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>27</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>36</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>126</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>24</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>30</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>49</v>
       </c>
       <c r="K18" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>134</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3">
+        <v>23</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>27</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="K20" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>143</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
@@ -2933,10 +2829,10 @@
         <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K21" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -2944,276 +2840,276 @@
         <v>145</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K22" s="3">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="K23" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="K24" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>50</v>
+        <v>162</v>
       </c>
       <c r="K25" s="3">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="K26" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="K27" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="3">
+        <v>10</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="3">
-        <v>16</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="K28" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>10</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="3">
-        <v>13</v>
-      </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="K29" s="3">
         <v>12</v>
@@ -3221,112 +3117,112 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>56</v>
+        <v>188</v>
       </c>
       <c r="K30" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
+        <v>10</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K31" s="3">
         <v>13</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K31" s="3">
-        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>192</v>
+        <v>93</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>193</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="K32" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>196</v>
@@ -3335,28 +3231,28 @@
         <v>197</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>199</v>
+        <v>67</v>
       </c>
       <c r="K33" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -3373,25 +3269,25 @@
         <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>203</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>204</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K34" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
@@ -3399,115 +3295,115 @@
         <v>205</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>62</v>
+        <v>210</v>
       </c>
       <c r="K35" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>212</v>
+        <v>139</v>
       </c>
       <c r="K36" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>213</v>
+        <v>163</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3">
+        <v>6</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>10</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G37" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="K37" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>219</v>
+        <v>58</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3519,19 +3415,19 @@
         <v>220</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>221</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="K38" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -3551,33 +3447,33 @@
         <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>227</v>
+        <v>67</v>
       </c>
       <c r="K39" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3586,582 +3482,306 @@
         <v>6</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="K40" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E41" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="K41" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" s="3">
-        <v>6</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="K42" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>242</v>
+        <v>44</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>142</v>
+        <v>231</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="K43" s="3">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="K44" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>76</v>
+        <v>247</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="K45" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>219</v>
+        <v>100</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>212</v>
+        <v>55</v>
       </c>
       <c r="K46" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="K47" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>261</v>
+        <v>88</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>95</v>
+        <v>257</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="K48" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E49" s="3">
-        <v>4</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" s="3">
-        <v>4</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K50" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E51" s="3">
-        <v>3</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K51" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="3">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="K52" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="3">
-        <v>3</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K53" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="3">
-        <v>3</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K54" s="3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E55" s="3">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K55" s="3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E56" s="3">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K56" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K56"/>
+  <autoFilter ref="A1:K48"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4210,14 +3830,6 @@
     <hyperlink ref="I46" r:id="rId45"/>
     <hyperlink ref="I47" r:id="rId46"/>
     <hyperlink ref="I48" r:id="rId47"/>
-    <hyperlink ref="I49" r:id="rId48"/>
-    <hyperlink ref="I50" r:id="rId49"/>
-    <hyperlink ref="I51" r:id="rId50"/>
-    <hyperlink ref="I52" r:id="rId51"/>
-    <hyperlink ref="I53" r:id="rId52"/>
-    <hyperlink ref="I54" r:id="rId53"/>
-    <hyperlink ref="I55" r:id="rId54"/>
-    <hyperlink ref="I56" r:id="rId55"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4225,7 +3837,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="29" customWidth="1"/>
+    <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -4236,174 +3848,78 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>253</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3">
-        <v>51</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3">
-        <v>36</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3">
-        <v>32</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="3">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4418,112 +3934,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>291</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>292</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>293</v>
+        <v>255</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>295</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>296</v>
+        <v>266</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>297</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>298</v>
+        <v>182</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>278</v>
+        <v>156</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="B10" s="3">
         <v>9</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>304</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
@@ -4531,65 +4047,65 @@
         <v>274</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>306</v>
+        <v>243</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>312</v>
+        <v>281</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>313</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>315</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -4606,13 +4122,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>316</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>317</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2">
@@ -4620,10 +4136,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>318</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -4631,10 +4147,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>319</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
@@ -4642,10 +4158,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>320</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5">
@@ -4656,7 +4172,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6">
@@ -4667,18 +4183,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>323</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -4696,51 +4201,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>324</v>
+        <v>292</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>325</v>
+        <v>293</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3">
         <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="D4" s="3"/>
     </row>
